--- a/scenario_data/SA_reagents_lcis.xlsx
+++ b/scenario_data/SA_reagents_lcis.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="470" documentId="13_ncr:1_{C4524105-2536-4029-AB93-C7F480F6810B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5724D54A-1459-48CB-AA8B-C43A8532FC67}"/>
+  <xr:revisionPtr revIDLastSave="490" documentId="13_ncr:1_{C4524105-2536-4029-AB93-C7F480F6810B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94E35EAA-3160-4C74-A26D-1737C032E0A1}"/>
   <bookViews>
-    <workbookView xWindow="210" yWindow="765" windowWidth="21795" windowHeight="18750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="585" windowWidth="28800" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -186,9 +186,6 @@
     <t>soda ash, light</t>
   </si>
   <si>
-    <t>ei_cutoff_3.10_remind_SSP2-NDC_2035_STEPS 2025-11-14</t>
-  </si>
-  <si>
     <t>market for sodium chloride, brine solution</t>
   </si>
   <si>
@@ -219,9 +216,6 @@
     <t>Water</t>
   </si>
   <si>
-    <t>biosphere3</t>
-  </si>
-  <si>
     <t>biosphere</t>
   </si>
   <si>
@@ -241,6 +235,12 @@
   </si>
   <si>
     <t>market for soda ash, light (prospective)</t>
+  </si>
+  <si>
+    <t>ei_cutoff_3.10_remind_SSP2-NDC_2035_NationalPlans 2026-05-29</t>
+  </si>
+  <si>
+    <t>ecoinvent-3.10.1-biosphere</t>
   </si>
 </sst>
 </file>
@@ -790,7 +790,7 @@
         <v>15</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>16</v>
@@ -806,7 +806,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K2" s="9">
         <v>1.8180000000000001</v>
@@ -874,7 +874,7 @@
         <v>15</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>4</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K3" s="9">
         <v>0.03</v>
@@ -958,7 +958,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>19</v>
@@ -973,7 +973,7 @@
         <v>4</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K4" s="9">
         <v>1.0263028649966146</v>
@@ -1041,7 +1041,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>21</v>
@@ -1056,7 +1056,7 @@
         <v>4</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K5" s="9">
         <v>1.4209375547956826</v>
@@ -1124,7 +1124,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>47</v>
@@ -1139,7 +1139,7 @@
         <v>4</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K6" s="9">
         <v>0.24754889176260042</v>
@@ -1207,7 +1207,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>48</v>
@@ -1222,7 +1222,7 @@
         <v>4</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K7" s="9">
         <v>5.3961626495443227E-2</v>
@@ -1290,7 +1290,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>23</v>
@@ -1305,7 +1305,7 @@
         <v>4</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K8" s="9">
         <v>0.45124906194963615</v>
@@ -1373,7 +1373,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
         <v>24</v>
@@ -1388,7 +1388,7 @@
         <v>4</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K9" s="9">
         <v>-1.8180000000000002E-2</v>
@@ -1494,7 +1494,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>16</v>
@@ -1510,7 +1510,7 @@
         <v>4</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K11" s="9">
         <v>1.8180000000000001</v>
@@ -1578,7 +1578,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>10</v>
@@ -1594,7 +1594,7 @@
         <v>4</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K12" s="9">
         <v>0.19093333333333334</v>
@@ -1662,7 +1662,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>19</v>
@@ -1678,7 +1678,7 @@
         <v>4</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K13" s="9">
         <v>1.0263028649966146</v>
@@ -1746,7 +1746,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>21</v>
@@ -1762,7 +1762,7 @@
         <v>4</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K14" s="9">
         <v>1.4209375547956826</v>
@@ -1830,7 +1830,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>47</v>
@@ -1846,7 +1846,7 @@
         <v>4</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K15" s="9">
         <v>0.24754889176260042</v>
@@ -1914,7 +1914,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E16" s="16" t="s">
         <v>48</v>
@@ -1930,7 +1930,7 @@
         <v>4</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K16" s="9">
         <v>5.3961626495443227E-2</v>
@@ -1998,7 +1998,7 @@
         <v>15</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>23</v>
@@ -2014,7 +2014,7 @@
         <v>4</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K17" s="9">
         <v>0.45124906194963615</v>
@@ -2082,7 +2082,7 @@
         <v>15</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
         <v>24</v>
@@ -2098,7 +2098,7 @@
         <v>4</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K18" s="9">
         <v>-1.8180000000000002E-2</v>
@@ -2204,7 +2204,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>14</v>
@@ -2219,7 +2219,7 @@
         <v>4</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K20" s="9">
         <v>0.85</v>
@@ -2287,7 +2287,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>26</v>
@@ -2302,7 +2302,7 @@
         <v>4</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K21" s="9">
         <v>0.15</v>
@@ -2408,7 +2408,7 @@
         <v>15</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E23" t="s">
         <v>16</v>
@@ -2422,8 +2422,8 @@
       <c r="I23" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J23" t="s">
-        <v>51</v>
+      <c r="J23" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K23" s="17">
         <v>1.1000000000000001</v>
@@ -2491,13 +2491,13 @@
         <v>15</v>
       </c>
       <c r="D24" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" t="s">
         <v>51</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>52</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
@@ -2505,8 +2505,8 @@
       <c r="I24" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J24" t="s">
-        <v>51</v>
+      <c r="J24" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K24" s="17">
         <v>1.5</v>
@@ -2574,13 +2574,13 @@
         <v>15</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E25" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" t="s">
         <v>54</v>
-      </c>
-      <c r="F25" t="s">
-        <v>55</v>
       </c>
       <c r="G25" t="s">
         <v>18</v>
@@ -2588,8 +2588,8 @@
       <c r="I25" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J25" t="s">
-        <v>51</v>
+      <c r="J25" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K25" s="17">
         <v>8.0000000000000004E-4</v>
@@ -2657,13 +2657,13 @@
         <v>15</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E26" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" t="s">
         <v>56</v>
-      </c>
-      <c r="F26" t="s">
-        <v>57</v>
       </c>
       <c r="G26" t="s">
         <v>18</v>
@@ -2671,8 +2671,8 @@
       <c r="I26" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J26" t="s">
-        <v>51</v>
+      <c r="J26" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K26" s="17">
         <v>2.0370370370370372</v>
@@ -2740,7 +2740,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
@@ -2754,8 +2754,8 @@
       <c r="I27" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J27" t="s">
-        <v>51</v>
+      <c r="J27" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K27" s="17">
         <v>0.30555555555555558</v>
@@ -2823,7 +2823,7 @@
         <v>15</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E28" t="s">
         <v>21</v>
@@ -2837,8 +2837,8 @@
       <c r="I28" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J28" t="s">
-        <v>51</v>
+      <c r="J28" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K28" s="17">
         <v>4.583333333333333</v>
@@ -2906,7 +2906,7 @@
         <v>15</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E29" t="s">
         <v>23</v>
@@ -2920,8 +2920,8 @@
       <c r="I29" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J29" t="s">
-        <v>51</v>
+      <c r="J29" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K29" s="17">
         <v>1.2222222222222223</v>
@@ -2989,7 +2989,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -3003,8 +3003,8 @@
       <c r="I30" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J30" t="s">
-        <v>51</v>
+      <c r="J30" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K30" s="17">
         <v>0.05</v>
@@ -3072,10 +3072,10 @@
         <v>15</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F31" t="s">
         <v>25</v>
@@ -3086,8 +3086,8 @@
       <c r="I31" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J31" t="s">
-        <v>51</v>
+      <c r="J31" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K31" s="17">
         <v>-6.0000000000000005E-2</v>
@@ -3155,19 +3155,19 @@
         <v>15</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H32" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J32" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K32" s="17">
         <f>0.555555555555555/1000</f>
@@ -3244,19 +3244,19 @@
         <v>15</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H33" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J33" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K33" s="17">
         <f>46.2962962962963/1000</f>
@@ -3333,19 +3333,19 @@
         <v>15</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E34" t="s">
+        <v>60</v>
+      </c>
+      <c r="H34" t="s">
+        <v>63</v>
+      </c>
+      <c r="I34" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H34" t="s">
-        <v>65</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>63</v>
-      </c>
       <c r="J34" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K34" s="17">
         <f>42.6634259259259/1000</f>
@@ -3422,19 +3422,19 @@
         <v>15</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E35" t="s">
+        <v>60</v>
+      </c>
+      <c r="H35" t="s">
+        <v>64</v>
+      </c>
+      <c r="I35" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H35" t="s">
-        <v>66</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>63</v>
-      </c>
       <c r="J35" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K35" s="17">
         <f>2.42916666666667/1000</f>
@@ -3540,7 +3540,7 @@
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B37" t="s">
         <v>50</v>
@@ -3549,7 +3549,7 @@
         <v>15</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E37" t="s">
         <v>16</v>
@@ -3563,8 +3563,8 @@
       <c r="I37" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J37" t="s">
-        <v>51</v>
+      <c r="J37" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K37" s="17">
         <v>1.1000000000000001</v>
@@ -3623,7 +3623,7 @@
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B38" t="s">
         <v>50</v>
@@ -3632,13 +3632,13 @@
         <v>15</v>
       </c>
       <c r="D38" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" t="s">
         <v>51</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>52</v>
-      </c>
-      <c r="F38" t="s">
-        <v>53</v>
       </c>
       <c r="G38" t="s">
         <v>15</v>
@@ -3646,8 +3646,8 @@
       <c r="I38" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J38" t="s">
-        <v>51</v>
+      <c r="J38" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K38" s="17">
         <v>1.5</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B39" t="s">
         <v>50</v>
@@ -3715,13 +3715,13 @@
         <v>15</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E39" t="s">
+        <v>53</v>
+      </c>
+      <c r="F39" t="s">
         <v>54</v>
-      </c>
-      <c r="F39" t="s">
-        <v>55</v>
       </c>
       <c r="G39" t="s">
         <v>18</v>
@@ -3729,8 +3729,8 @@
       <c r="I39" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J39" t="s">
-        <v>51</v>
+      <c r="J39" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K39" s="17">
         <v>8.0000000000000004E-4</v>
@@ -3789,7 +3789,7 @@
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B40" t="s">
         <v>50</v>
@@ -3798,13 +3798,13 @@
         <v>15</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E40" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40" t="s">
         <v>56</v>
-      </c>
-      <c r="F40" t="s">
-        <v>57</v>
       </c>
       <c r="G40" t="s">
         <v>18</v>
@@ -3812,8 +3812,8 @@
       <c r="I40" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J40" t="s">
-        <v>51</v>
+      <c r="J40" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K40" s="17">
         <v>2.0370370370370372</v>
@@ -3872,7 +3872,7 @@
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B41" t="s">
         <v>50</v>
@@ -3881,7 +3881,7 @@
         <v>15</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
@@ -3895,8 +3895,8 @@
       <c r="I41" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J41" t="s">
-        <v>51</v>
+      <c r="J41" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K41" s="17">
         <v>0.35348055555555558</v>
@@ -3955,7 +3955,7 @@
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B42" t="s">
         <v>50</v>
@@ -3964,7 +3964,7 @@
         <v>15</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E42" t="s">
         <v>21</v>
@@ -3978,8 +3978,8 @@
       <c r="I42" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J42" t="s">
-        <v>51</v>
+      <c r="J42" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K42" s="17">
         <v>5.3022083333333327</v>
@@ -4038,7 +4038,7 @@
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B43" t="s">
         <v>50</v>
@@ -4047,7 +4047,7 @@
         <v>15</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E43" t="s">
         <v>23</v>
@@ -4061,8 +4061,8 @@
       <c r="I43" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J43" t="s">
-        <v>51</v>
+      <c r="J43" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K43" s="17">
         <v>1.4139222222222223</v>
@@ -4121,7 +4121,7 @@
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B44" t="s">
         <v>50</v>
@@ -4130,7 +4130,7 @@
         <v>15</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
@@ -4144,8 +4144,8 @@
       <c r="I44" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J44" t="s">
-        <v>51</v>
+      <c r="J44" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K44" s="17">
         <v>7.9250000000000001E-2</v>
@@ -4204,7 +4204,7 @@
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B45" t="s">
         <v>50</v>
@@ -4213,10 +4213,10 @@
         <v>15</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F45" t="s">
         <v>25</v>
@@ -4227,8 +4227,8 @@
       <c r="I45" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J45" t="s">
-        <v>51</v>
+      <c r="J45" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K45" s="17">
         <v>-0.06</v>
@@ -4287,7 +4287,7 @@
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
         <v>50</v>
@@ -4296,19 +4296,19 @@
         <v>15</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H46" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J46" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K46" s="17">
         <f>0.555555555555555/1000</f>
@@ -4376,7 +4376,7 @@
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B47" t="s">
         <v>50</v>
@@ -4385,19 +4385,19 @@
         <v>15</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H47" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J47" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K47" s="17">
         <f>46.2962962962963/1000</f>
@@ -4465,7 +4465,7 @@
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B48" t="s">
         <v>50</v>
@@ -4474,19 +4474,19 @@
         <v>15</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E48" t="s">
+        <v>60</v>
+      </c>
+      <c r="H48" t="s">
+        <v>63</v>
+      </c>
+      <c r="I48" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H48" t="s">
-        <v>65</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>63</v>
-      </c>
       <c r="J48" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K48" s="17">
         <f>42.6634259259259/1000</f>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B49" t="s">
         <v>50</v>
@@ -4563,19 +4563,19 @@
         <v>15</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E49" t="s">
+        <v>60</v>
+      </c>
+      <c r="H49" t="s">
+        <v>64</v>
+      </c>
+      <c r="I49" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H49" t="s">
-        <v>66</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>63</v>
-      </c>
       <c r="J49" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K49" s="17">
         <f>2.42916666666667/1000</f>
@@ -4681,7 +4681,7 @@
     </row>
     <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B51" t="s">
         <v>50</v>
@@ -4690,7 +4690,7 @@
         <v>15</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E51" t="s">
         <v>19</v>
@@ -4704,8 +4704,8 @@
       <c r="I51" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J51" t="s">
-        <v>51</v>
+      <c r="J51" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K51" s="17">
         <v>0.11141661725129415</v>
@@ -4764,7 +4764,7 @@
     </row>
     <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B52" t="s">
         <v>50</v>
@@ -4773,7 +4773,7 @@
         <v>15</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E52" t="s">
         <v>21</v>
@@ -4787,8 +4787,8 @@
       <c r="I52" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J52" t="s">
-        <v>51</v>
+      <c r="J52" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K52" s="17">
         <v>1.6712492587694121</v>
@@ -4847,7 +4847,7 @@
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B53" t="s">
         <v>50</v>
@@ -4856,7 +4856,7 @@
         <v>15</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E53" t="s">
         <v>23</v>
@@ -4870,8 +4870,8 @@
       <c r="I53" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J53" t="s">
-        <v>51</v>
+      <c r="J53" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K53" s="17">
         <v>0.44566646900517659</v>
@@ -4930,7 +4930,7 @@
     </row>
     <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B54" t="s">
         <v>50</v>
@@ -4939,19 +4939,19 @@
         <v>15</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E54" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H54" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J54" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K54" s="18">
         <v>1.7212500000000001E-3</v>
@@ -5010,7 +5010,7 @@
     </row>
     <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B55" t="s">
         <v>50</v>
@@ -5019,19 +5019,19 @@
         <v>15</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E55" t="s">
+        <v>60</v>
+      </c>
+      <c r="H55" t="s">
+        <v>63</v>
+      </c>
+      <c r="I55" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H55" t="s">
-        <v>65</v>
-      </c>
-      <c r="I55" s="7" t="s">
-        <v>63</v>
-      </c>
       <c r="J55" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K55" s="18">
         <v>2.5818750000000001E-4</v>
@@ -5090,7 +5090,7 @@
     </row>
     <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B56" t="s">
         <v>50</v>
@@ -5099,19 +5099,19 @@
         <v>15</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E56" t="s">
+        <v>60</v>
+      </c>
+      <c r="H56" t="s">
+        <v>64</v>
+      </c>
+      <c r="I56" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H56" t="s">
-        <v>66</v>
-      </c>
-      <c r="I56" s="7" t="s">
-        <v>63</v>
-      </c>
       <c r="J56" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K56" s="18">
         <v>1.03275E-3</v>
@@ -5208,7 +5208,7 @@
     </row>
     <row r="58" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B58" t="s">
         <v>50</v>
@@ -5217,7 +5217,7 @@
         <v>15</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E58" t="s">
         <v>49</v>
@@ -5231,8 +5231,8 @@
       <c r="I58" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J58" t="s">
-        <v>51</v>
+      <c r="J58" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K58" s="17">
         <v>0.52495619606900867</v>
@@ -5297,7 +5297,7 @@
     </row>
     <row r="59" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B59" t="s">
         <v>50</v>
@@ -5306,10 +5306,10 @@
         <v>15</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E59" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F59" t="s">
         <v>50</v>
@@ -5320,8 +5320,8 @@
       <c r="I59" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J59" t="s">
-        <v>51</v>
+      <c r="J59" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K59" s="17">
         <v>9.2639328718060354E-2</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="60" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B60" t="s">
         <v>50</v>
@@ -5395,10 +5395,10 @@
         <v>15</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E60" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F60" t="s">
         <v>50</v>
@@ -5409,8 +5409,8 @@
       <c r="I60" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J60" t="s">
-        <v>51</v>
+      <c r="J60" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="K60" s="17">
         <v>0.38240447521293092</v>
